--- a/data/trans_orig/IMC_inf_MED_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R2-Provincia-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>16566</v>
+        <v>25349</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11514</v>
+        <v>19433</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>21540</v>
+        <v>31817</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.4612795032128404</v>
+        <v>0.4722952555714748</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3206187475257563</v>
+        <v>0.3620667884427706</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.5997887693352357</v>
+        <v>0.5928000859434656</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>13205</v>
+        <v>20034</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>8962</v>
+        <v>14434</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>17279</v>
+        <v>25086</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4150075702086364</v>
+        <v>0.4361174503586625</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2816535332917799</v>
+        <v>0.3142053165494396</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.543043996044576</v>
+        <v>0.5461057107573494</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>29771</v>
+        <v>45383</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>23660</v>
+        <v>36613</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>37253</v>
+        <v>53119</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4395422471388949</v>
+        <v>0.4556109464731452</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3493244512298525</v>
+        <v>0.3675660541829899</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5500188948178931</v>
+        <v>0.5332772012998677</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>19347</v>
+        <v>28323</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>14373</v>
+        <v>21855</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>24399</v>
+        <v>34239</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.5387204967871596</v>
+        <v>0.5277047444285252</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4002112306647642</v>
+        <v>0.4071999140565346</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6793812524742436</v>
+        <v>0.6379332115572295</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>18613</v>
+        <v>25903</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14539</v>
+        <v>20851</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>22856</v>
+        <v>31503</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5849924297913637</v>
+        <v>0.5638825496413374</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4569560039554239</v>
+        <v>0.4538942892426506</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.7183464667082201</v>
+        <v>0.6857946834505602</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>37960</v>
+        <v>54226</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>30478</v>
+        <v>46490</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>44071</v>
+        <v>62996</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5604577528611051</v>
+        <v>0.5443890535268548</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4499811051821072</v>
+        <v>0.4667227987001322</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.6506755487701474</v>
+        <v>0.6324339458170097</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>35913</v>
+        <v>53672</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35913</v>
+        <v>53672</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>35913</v>
+        <v>53672</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>31818</v>
+        <v>45937</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>31818</v>
+        <v>45937</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>31818</v>
+        <v>45937</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>67731</v>
+        <v>99609</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>67731</v>
+        <v>99609</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>67731</v>
+        <v>99609</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>40932</v>
+        <v>46765</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>33945</v>
+        <v>38930</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>48475</v>
+        <v>54379</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5036244304466816</v>
+        <v>0.491007065732988</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4176595977068927</v>
+        <v>0.4087430987615043</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5964336859113883</v>
+        <v>0.5709493518761287</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>30227</v>
+        <v>37406</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>23926</v>
+        <v>29799</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>36994</v>
+        <v>45080</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.408057725170147</v>
+        <v>0.4320889327694836</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.322996468350061</v>
+        <v>0.3442237334362889</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4994048491779128</v>
+        <v>0.5207462459031099</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>71159</v>
+        <v>84171</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>60867</v>
+        <v>73755</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>81473</v>
+        <v>95489</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4580555470669411</v>
+        <v>0.4629533984256314</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3918057414148061</v>
+        <v>0.4056654177790158</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5244461180650692</v>
+        <v>0.5252019639097362</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>40343</v>
+        <v>48478</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>32800</v>
+        <v>40864</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>47330</v>
+        <v>56313</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4963755695533184</v>
+        <v>0.508992934267012</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4035663140886116</v>
+        <v>0.4290506481238713</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.5823404022931072</v>
+        <v>0.5912569012384956</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>43849</v>
+        <v>49163</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>37082</v>
+        <v>41489</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>50150</v>
+        <v>56770</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.591942274829853</v>
+        <v>0.5679110672305164</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5005951508220871</v>
+        <v>0.4792537540968901</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6770035316499391</v>
+        <v>0.6557762665637105</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>84192</v>
+        <v>97642</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>73878</v>
+        <v>86324</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>94484</v>
+        <v>108058</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.5419444529330589</v>
+        <v>0.5370466015743686</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.4755538819349305</v>
+        <v>0.4747980360902639</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6081942585851939</v>
+        <v>0.5943345822209842</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>81275</v>
+        <v>95243</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>81275</v>
+        <v>95243</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>81275</v>
+        <v>95243</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>74076</v>
+        <v>86569</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>74076</v>
+        <v>86569</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>74076</v>
+        <v>86569</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>155351</v>
+        <v>181813</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>155351</v>
+        <v>181813</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>155351</v>
+        <v>181813</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>27592</v>
+        <v>31080</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>21604</v>
+        <v>24390</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>33866</v>
+        <v>37053</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.524396333260804</v>
+        <v>0.5160022930326313</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4106061651640907</v>
+        <v>0.4049208209204359</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.6436400058085306</v>
+        <v>0.6151652247051465</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>28169</v>
+        <v>30360</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>21789</v>
+        <v>23280</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>33627</v>
+        <v>36244</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5534837931667934</v>
+        <v>0.5178646491574784</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.4281206889118948</v>
+        <v>0.397095166574539</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6607271144915651</v>
+        <v>0.6182265381086729</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>55761</v>
+        <v>61441</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>47584</v>
+        <v>51278</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>64607</v>
+        <v>69658</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.5386979991512685</v>
+        <v>0.5169208814928512</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.4597064837745383</v>
+        <v>0.4314143219126282</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.6241610115453644</v>
+        <v>0.586055017404283</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>25024</v>
+        <v>29153</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>18750</v>
+        <v>23180</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>31012</v>
+        <v>35843</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.475603666739196</v>
+        <v>0.4839977069673687</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.3563599941914692</v>
+        <v>0.3848347752948535</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.589393834835909</v>
+        <v>0.595079179079564</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>22725</v>
+        <v>28266</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>17267</v>
+        <v>22382</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>29105</v>
+        <v>35346</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4465162068332066</v>
+        <v>0.4821353508425216</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3392728855084349</v>
+        <v>0.381773461891327</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.5718793110881053</v>
+        <v>0.602904833425461</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>47749</v>
+        <v>57419</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>38903</v>
+        <v>49202</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>55926</v>
+        <v>67582</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.4613020008487315</v>
+        <v>0.4830791185071488</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.3758389884546356</v>
+        <v>0.4139449825957172</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.5402935162254622</v>
+        <v>0.5685856780873723</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>52616</v>
+        <v>60233</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>52616</v>
+        <v>60233</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>52616</v>
+        <v>60233</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>50894</v>
+        <v>58626</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>50894</v>
+        <v>58626</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>50894</v>
+        <v>58626</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>103510</v>
+        <v>118860</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>103510</v>
+        <v>118860</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>103510</v>
+        <v>118860</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>31076</v>
+        <v>38245</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>25035</v>
+        <v>30824</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>37566</v>
+        <v>44604</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5525187038294651</v>
+        <v>0.551741589565084</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4451082532031457</v>
+        <v>0.4446755577949175</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.667913100075931</v>
+        <v>0.6434719453400058</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>19996</v>
+        <v>21758</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>14497</v>
+        <v>15829</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>26077</v>
+        <v>28266</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3880922585261118</v>
+        <v>0.3513104310695965</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2813509077373829</v>
+        <v>0.255578277979367</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5061132899433084</v>
+        <v>0.4563769766950463</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>51072</v>
+        <v>60003</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>42188</v>
+        <v>50861</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>59928</v>
+        <v>70219</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4739054843451959</v>
+        <v>0.4571623170991999</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3914714436407796</v>
+        <v>0.3875094226603834</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5560815310776955</v>
+        <v>0.5349970966295287</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>25168</v>
+        <v>31072</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>18678</v>
+        <v>24713</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>31209</v>
+        <v>38493</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4474812961705349</v>
+        <v>0.4482584104349159</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.332086899924069</v>
+        <v>0.3565280546599944</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.5548917467968543</v>
+        <v>0.5553244422050825</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>31529</v>
+        <v>40177</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25448</v>
+        <v>33669</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>37028</v>
+        <v>46106</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6119077414738882</v>
+        <v>0.6486895689304034</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4938867100566915</v>
+        <v>0.5436230233049536</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7186490922626172</v>
+        <v>0.7444217220206331</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>56697</v>
+        <v>71249</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>47841</v>
+        <v>61033</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>65581</v>
+        <v>80391</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5260945156548041</v>
+        <v>0.5428376829008001</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4439184689223046</v>
+        <v>0.4650029033704715</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6085285563592204</v>
+        <v>0.6124905773396172</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>56244</v>
+        <v>69317</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>56244</v>
+        <v>69317</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>56244</v>
+        <v>69317</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>51525</v>
+        <v>61935</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>51525</v>
+        <v>61935</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>51525</v>
+        <v>61935</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>107769</v>
+        <v>131252</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>107769</v>
+        <v>131252</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>107769</v>
+        <v>131252</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>16923</v>
+        <v>17729</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>12182</v>
+        <v>12098</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>21226</v>
+        <v>22319</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.5632867490828281</v>
+        <v>0.4508436287513464</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.4054806254752397</v>
+        <v>0.3076568333432102</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.706512006368739</v>
+        <v>0.5675934358252114</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>13050</v>
+        <v>20041</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>8605</v>
+        <v>14439</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>18015</v>
+        <v>25285</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4880157311884761</v>
+        <v>0.494869922808184</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3217850375214405</v>
+        <v>0.3565416382702931</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.6737146902952583</v>
+        <v>0.6243625410451809</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>29972</v>
+        <v>37769</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>23991</v>
+        <v>30546</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>36122</v>
+        <v>45927</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.5278406551120686</v>
+        <v>0.4731805039153537</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.4225052058721836</v>
+        <v>0.3826815882171398</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.6361356689561104</v>
+        <v>0.5753764379605452</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>13120</v>
+        <v>21594</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>8817</v>
+        <v>17004</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>17861</v>
+        <v>27225</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4367132509171719</v>
+        <v>0.5491563712486536</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.293487993631261</v>
+        <v>0.4324065641747884</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5945193745247601</v>
+        <v>0.6923431666567899</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>13690</v>
+        <v>20456</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>8725</v>
+        <v>15212</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>18135</v>
+        <v>26058</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5119842688115239</v>
+        <v>0.505130077191816</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3262853097047415</v>
+        <v>0.375637458954819</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.6782149624785593</v>
+        <v>0.6434583617297069</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>26811</v>
+        <v>42051</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>20661</v>
+        <v>33893</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>32792</v>
+        <v>49274</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.4721593448879314</v>
+        <v>0.5268194960846463</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.3638643310438896</v>
+        <v>0.4246235620394548</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.5774947941278166</v>
+        <v>0.6173184117828604</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>30043</v>
+        <v>39323</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>30043</v>
+        <v>39323</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>30043</v>
+        <v>39323</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>26740</v>
+        <v>40497</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>26740</v>
+        <v>40497</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>26740</v>
+        <v>40497</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>56783</v>
+        <v>79820</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>56783</v>
+        <v>79820</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>56783</v>
+        <v>79820</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1814,67 +1814,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>16328</v>
+        <v>21211</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>11321</v>
+        <v>15378</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>21538</v>
+        <v>27136</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.3918236574457624</v>
+        <v>0.4349233288329477</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.2716809408270157</v>
+        <v>0.3153209800378932</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5168452408577144</v>
+        <v>0.5564133849630158</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>19166</v>
+        <v>21882</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>13908</v>
+        <v>16388</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>24191</v>
+        <v>27603</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.4350420523546132</v>
+        <v>0.4678465462018038</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3156856496850026</v>
+        <v>0.3503931498939412</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.549118718352628</v>
+        <v>0.5901649996259077</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>35493</v>
+        <v>43092</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>28364</v>
+        <v>34006</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>43237</v>
+        <v>50360</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.4140335658462114</v>
+        <v>0.4510406139316008</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.3308629201222468</v>
+        <v>0.3559379628374764</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5043571773740811</v>
+        <v>0.5271138713332993</v>
       </c>
     </row>
     <row r="20">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>25344</v>
+        <v>27558</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>20134</v>
+        <v>21633</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>30351</v>
+        <v>33391</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6081763425542376</v>
+        <v>0.5650766711670523</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.4831547591422855</v>
+        <v>0.4435866150369858</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.7283190591729839</v>
+        <v>0.6846790199621072</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>35</v>
@@ -1912,40 +1912,40 @@
         <v>24889</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>19864</v>
+        <v>19168</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>30147</v>
+        <v>30383</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.5649579476453868</v>
+        <v>0.5321534537981962</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.4508812816473718</v>
+        <v>0.409835000374092</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.684314350314997</v>
+        <v>0.6496068501060585</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>50233</v>
+        <v>52447</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>42489</v>
+        <v>45179</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>57362</v>
+        <v>61533</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.5859664341537887</v>
+        <v>0.5489593860683992</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.495642822625919</v>
+        <v>0.4728861286667007</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.6691370798777533</v>
+        <v>0.6440620371625236</v>
       </c>
     </row>
     <row r="21">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>41672</v>
+        <v>48769</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>41672</v>
+        <v>48769</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>41672</v>
+        <v>48769</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1977,16 +1977,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>44055</v>
+        <v>46771</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>44055</v>
+        <v>46771</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>44055</v>
+        <v>46771</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1998,16 +1998,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>85726</v>
+        <v>95539</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>85726</v>
+        <v>95539</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>85726</v>
+        <v>95539</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2031,67 +2031,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>61249</v>
+        <v>66211</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>52798</v>
+        <v>57306</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>68741</v>
+        <v>75143</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.584200569214791</v>
+        <v>0.5624001477972072</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.5036001864474948</v>
+        <v>0.4867591143230816</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.6556622390002919</v>
+        <v>0.6382670633063507</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>41330</v>
+        <v>46383</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>33249</v>
+        <v>38484</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>49928</v>
+        <v>55574</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.3969761595117522</v>
+        <v>0.4059530344023145</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.3193576495699489</v>
+        <v>0.3368208811750535</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.4795591070749122</v>
+        <v>0.4863950413948797</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>102579</v>
+        <v>112594</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>90677</v>
+        <v>101831</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>114133</v>
+        <v>125741</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.4909149819528746</v>
+        <v>0.4853478270515801</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.4339558561018683</v>
+        <v>0.4389510773369885</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.546207604932421</v>
+        <v>0.5420190178900705</v>
       </c>
     </row>
     <row r="23">
@@ -2102,67 +2102,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>43593</v>
+        <v>51519</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>36101</v>
+        <v>42587</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52044</v>
+        <v>60424</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.4157994307852089</v>
+        <v>0.4375998522027928</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.3443377609997082</v>
+        <v>0.3617329366936493</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.4963998135525062</v>
+        <v>0.5132408856769185</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>62783</v>
+        <v>67873</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>54185</v>
+        <v>58682</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>70864</v>
+        <v>75772</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.6030238404882478</v>
+        <v>0.5940469655976854</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.5204408929250874</v>
+        <v>0.5136049586051199</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.6806423504300511</v>
+        <v>0.6631791188249463</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>106376</v>
+        <v>119392</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>94822</v>
+        <v>106245</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>118278</v>
+        <v>130155</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.5090850180471254</v>
+        <v>0.5146521729484199</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.4537923950675791</v>
+        <v>0.4579809821099297</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.5660441438981317</v>
+        <v>0.5610489226630117</v>
       </c>
     </row>
     <row r="24">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>104842</v>
+        <v>117730</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>104842</v>
+        <v>117730</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>104842</v>
+        <v>117730</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -2194,16 +2194,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>104113</v>
+        <v>114256</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>104113</v>
+        <v>114256</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>104113</v>
+        <v>114256</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -2215,16 +2215,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>208955</v>
+        <v>231986</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>208955</v>
+        <v>231986</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>208955</v>
+        <v>231986</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -2248,67 +2248,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>70251</v>
+        <v>78489</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>61718</v>
+        <v>68677</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>78682</v>
+        <v>87725</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5823738072215981</v>
+        <v>0.5543852012649367</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.511638159903209</v>
+        <v>0.4850761422521752</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.6522726137221292</v>
+        <v>0.6196164612111316</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>60371</v>
+        <v>69288</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>50816</v>
+        <v>59796</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>68650</v>
+        <v>79095</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.5140182526764392</v>
+        <v>0.4893349949007043</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4326633267526577</v>
+        <v>0.4222974978204725</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.584501102198059</v>
+        <v>0.5585984966336142</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>130622</v>
+        <v>147777</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>117507</v>
+        <v>134314</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>142448</v>
+        <v>162191</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5486523225401284</v>
+        <v>0.5218581533889352</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4935647460180483</v>
+        <v>0.4743152417103469</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5983246553601281</v>
+        <v>0.5727572142120235</v>
       </c>
     </row>
     <row r="26">
@@ -2319,67 +2319,67 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>50377</v>
+        <v>63090</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>41946</v>
+        <v>53854</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>58910</v>
+        <v>72902</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.4176261927784019</v>
+        <v>0.4456147987350633</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.3477273862778708</v>
+        <v>0.3803835387888685</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.488361840096791</v>
+        <v>0.5149238577478249</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>57079</v>
+        <v>72308</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>48800</v>
+        <v>62501</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>66634</v>
+        <v>81800</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.4859817473235608</v>
+        <v>0.5106650050992957</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4154988978019409</v>
+        <v>0.4414015033663859</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.5673366732473414</v>
+        <v>0.5777025021795279</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>107456</v>
+        <v>135398</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>95630</v>
+        <v>120984</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>120571</v>
+        <v>148861</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.4513476774598715</v>
+        <v>0.4781418466110648</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.4016753446398719</v>
+        <v>0.4272427857879765</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.5064352539819518</v>
+        <v>0.5256847582896531</v>
       </c>
     </row>
     <row r="27">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>120628</v>
+        <v>141579</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>120628</v>
+        <v>141579</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>120628</v>
+        <v>141579</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2411,16 +2411,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>117450</v>
+        <v>141596</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>117450</v>
+        <v>141596</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>117450</v>
+        <v>141596</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2432,16 +2432,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>238078</v>
+        <v>283175</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>238078</v>
+        <v>283175</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>238078</v>
+        <v>283175</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2465,67 +2465,67 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>262560</v>
+        <v>303500</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>301398</v>
+        <v>345372</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.5368847747166713</v>
+        <v>0.5194073618784171</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.5018018298204001</v>
+        <v>0.4849276368679208</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.5760283859890361</v>
+        <v>0.5518300341758322</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>506430</v>
+        <v>592231</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>481200</v>
+        <v>564377</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>532083</v>
+        <v>621068</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.4946073589230291</v>
+        <v>0.4846192482017541</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.4699657488694993</v>
+        <v>0.4618263964367272</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.5196611328841555</v>
+        <v>0.5082161603494973</v>
       </c>
     </row>
     <row r="29">
@@ -2536,67 +2536,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>349</v>
+        <v>434</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>242318</v>
+        <v>300787</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>221836</v>
+        <v>280494</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>260674</v>
+        <v>322366</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.4631152252833288</v>
+        <v>0.4805926381215829</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.423971614010964</v>
+        <v>0.448169965824168</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.4981981701795999</v>
+        <v>0.5150723631320794</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>396</v>
+        <v>473</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>275156</v>
+        <v>329037</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>256569</v>
+        <v>308902</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>293350</v>
+        <v>349592</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.5495753939059956</v>
+        <v>0.5519006187905663</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.5124510828227896</v>
+        <v>0.5181286473350197</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.5859139402897362</v>
+        <v>0.5863781379423997</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>745</v>
+        <v>907</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>517474</v>
+        <v>629823</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>491821</v>
+        <v>600986</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>542704</v>
+        <v>657677</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.5053926410769709</v>
+        <v>0.5153807517982459</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.4803388671158446</v>
+        <v>0.4917838396505027</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.5300342511305007</v>
+        <v>0.5381736035632728</v>
       </c>
     </row>
     <row r="30">
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -2628,16 +2628,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>1</v>
@@ -2649,16 +2649,16 @@
         <v>1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>1</v>
@@ -2734,7 +2734,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2918,67 +2918,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>26858</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>20384</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>32653</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.5038681631579041</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3824151309727361</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.6125892627662518</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>17267</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>12674</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>21398</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.6014051133347678</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.4414294145813135</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0.7453027448281438</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>18</v>
-      </c>
       <c r="K4" s="5" t="n">
-        <v>11637</v>
+        <v>16986</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>7757</v>
+        <v>11930</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>15976</v>
+        <v>22889</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3920979648385204</v>
+        <v>0.3488890066472408</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2613710024826029</v>
+        <v>0.2450536212237205</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5383107570656324</v>
+        <v>0.4701368254333086</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>28904</v>
+        <v>43844</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>22598</v>
+        <v>35601</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>35199</v>
+        <v>51857</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4950181309602348</v>
+        <v>0.4298881746763392</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3870193879008262</v>
+        <v>0.3490704960211852</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.6028193733353759</v>
+        <v>0.5084528428363834</v>
       </c>
     </row>
     <row r="5">
@@ -2989,67 +2989,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>11444</v>
+        <v>26446</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7313</v>
+        <v>20651</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>16037</v>
+        <v>32920</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3985948866652322</v>
+        <v>0.4961318368420959</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2546972551718561</v>
+        <v>0.3874107372337482</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5585705854186862</v>
+        <v>0.6175848690272639</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>18041</v>
+        <v>31699</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13702</v>
+        <v>25796</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>21921</v>
+        <v>36755</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6079020351614796</v>
+        <v>0.6511109933527591</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4616892429343676</v>
+        <v>0.5298631745666914</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.7386289975173971</v>
+        <v>0.7549463787762798</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>29486</v>
+        <v>58145</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>23191</v>
+        <v>50132</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>35792</v>
+        <v>66388</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5049818690397652</v>
+        <v>0.5701118253236608</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.3971806266646239</v>
+        <v>0.4915471571636165</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.6129806120991738</v>
+        <v>0.6509295039788148</v>
       </c>
     </row>
     <row r="6">
@@ -3060,16 +3060,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>28711</v>
+        <v>53304</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>28711</v>
+        <v>53304</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>28711</v>
+        <v>53304</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -3081,16 +3081,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>29678</v>
+        <v>48685</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>29678</v>
+        <v>48685</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>29678</v>
+        <v>48685</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3102,16 +3102,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>58390</v>
+        <v>101989</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>58390</v>
+        <v>101989</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>58390</v>
+        <v>101989</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3135,67 +3135,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>42685</v>
+        <v>49287</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>35504</v>
+        <v>41457</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>49419</v>
+        <v>57082</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5382569652458234</v>
+        <v>0.4979558781208919</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4477107789206107</v>
+        <v>0.4188509188634996</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6231727849916974</v>
+        <v>0.5767128669569634</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>32249</v>
+        <v>38889</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>25009</v>
+        <v>31369</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>39435</v>
+        <v>46398</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4170018156258632</v>
+        <v>0.437756607468934</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3233816914243586</v>
+        <v>0.353105082344024</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5099296679535558</v>
+        <v>0.5222767055463395</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>74934</v>
+        <v>88176</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>65103</v>
+        <v>77236</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>85884</v>
+        <v>99078</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4783907122377126</v>
+        <v>0.4694811989109924</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4156286343593442</v>
+        <v>0.4112315615368583</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5482974219860421</v>
+        <v>0.5275293472699424</v>
       </c>
     </row>
     <row r="8">
@@ -3206,67 +3206,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>36617</v>
+        <v>49691</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>29883</v>
+        <v>41896</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>43798</v>
+        <v>57521</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4617430347541765</v>
+        <v>0.5020441218791081</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3768272150083026</v>
+        <v>0.4232871330430364</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.5522892210793897</v>
+        <v>0.5811490811365003</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>45086</v>
+        <v>49949</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>37900</v>
+        <v>42440</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>52326</v>
+        <v>57469</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5829981843741368</v>
+        <v>0.562243392531066</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4900703320464445</v>
+        <v>0.4777232944536605</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6766183085756415</v>
+        <v>0.646894917655976</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>81703</v>
+        <v>99640</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>70753</v>
+        <v>88738</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>91534</v>
+        <v>110580</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.5216092877622874</v>
+        <v>0.5305188010890076</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.4517025780139579</v>
+        <v>0.4724706527300576</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.5843713656406556</v>
+        <v>0.5887684384631416</v>
       </c>
     </row>
     <row r="9">
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>79302</v>
+        <v>98978</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>79302</v>
+        <v>98978</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>79302</v>
+        <v>98978</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3298,16 +3298,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>77335</v>
+        <v>88838</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>77335</v>
+        <v>88838</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>77335</v>
+        <v>88838</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3319,16 +3319,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>156637</v>
+        <v>187816</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>156637</v>
+        <v>187816</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>156637</v>
+        <v>187816</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3358,19 +3358,19 @@
         <v>21836</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>15406</v>
+        <v>15793</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>28142</v>
+        <v>28409</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3707423762256977</v>
+        <v>0.3582469424288311</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2615755516962056</v>
+        <v>0.2590941799668749</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4778137763637623</v>
+        <v>0.4660864857772939</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>23</v>
@@ -3379,19 +3379,19 @@
         <v>17756</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>12035</v>
+        <v>12347</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>23782</v>
+        <v>24841</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.317086248579467</v>
+        <v>0.312845210000638</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2149231833955695</v>
+        <v>0.2175484725475255</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4247019808937464</v>
+        <v>0.4376813520705679</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>53</v>
@@ -3400,19 +3400,19 @@
         <v>39592</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>31171</v>
+        <v>31616</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>48476</v>
+        <v>48345</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3445919455768914</v>
+        <v>0.3363555532448376</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2712960484273413</v>
+        <v>0.2686007372737053</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4219119531189583</v>
+        <v>0.4107231803145353</v>
       </c>
     </row>
     <row r="11">
@@ -3423,67 +3423,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>39117</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>32544</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>45160</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0.641753057571169</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.5339135142227061</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.7409058200331251</v>
+      </c>
+      <c r="J11" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>37062</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>30756</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>43492</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.6292576237743023</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>0.5221862236362379</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0.7384244483037945</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>51</v>
-      </c>
       <c r="K11" s="5" t="n">
-        <v>38240</v>
+        <v>38999</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>32214</v>
+        <v>31914</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>43961</v>
+        <v>44408</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6829137514205329</v>
+        <v>0.687154789999362</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.5752980191062534</v>
+        <v>0.5623186479294325</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7850768166044305</v>
+        <v>0.7824515274524748</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>75303</v>
+        <v>78116</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>66419</v>
+        <v>69363</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>83724</v>
+        <v>86092</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6554080544231086</v>
+        <v>0.6636444467551624</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5780880468810413</v>
+        <v>0.5892768196854646</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7287039515726585</v>
+        <v>0.7313992627262947</v>
       </c>
     </row>
     <row r="12">
@@ -3494,16 +3494,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>58898</v>
+        <v>60953</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>58898</v>
+        <v>60953</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>58898</v>
+        <v>60953</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3515,16 +3515,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>55996</v>
+        <v>56755</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>55996</v>
+        <v>56755</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>55996</v>
+        <v>56755</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3536,16 +3536,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>114895</v>
+        <v>117708</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>114895</v>
+        <v>117708</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>114895</v>
+        <v>117708</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -3569,67 +3569,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>20988</v>
+        <v>29460</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>15126</v>
+        <v>22634</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>26506</v>
+        <v>35856</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4799315775187655</v>
+        <v>0.5023048047176664</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3458922828201666</v>
+        <v>0.3859242223467234</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.6061100460283197</v>
+        <v>0.6113708275772135</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>13077</v>
+        <v>17562</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>8861</v>
+        <v>12580</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>18029</v>
+        <v>23042</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3781711730499282</v>
+        <v>0.3493209765359598</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2562544811785605</v>
+        <v>0.250210444072314</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5213883197571801</v>
+        <v>0.4583190462813571</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>34065</v>
+        <v>47022</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>27114</v>
+        <v>38003</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>41764</v>
+        <v>55169</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.434997818482946</v>
+        <v>0.4316927122852053</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3462396171963531</v>
+        <v>0.3488956651182488</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5333133991819685</v>
+        <v>0.5064914560438766</v>
       </c>
     </row>
     <row r="14">
@@ -3640,67 +3640,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>22743</v>
+        <v>29189</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17225</v>
+        <v>22793</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>28605</v>
+        <v>36015</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5200684224812345</v>
+        <v>0.4976951952823336</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.3938899539716801</v>
+        <v>0.3886291724227865</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6541077171798331</v>
+        <v>0.6140757776532767</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>21502</v>
+        <v>32714</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>16550</v>
+        <v>27234</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>25718</v>
+        <v>37696</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6218288269500718</v>
+        <v>0.6506790234640402</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4786116802428198</v>
+        <v>0.5416809537186426</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7437455188214397</v>
+        <v>0.7497895559276857</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>44245</v>
+        <v>61902</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>36546</v>
+        <v>53755</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>51196</v>
+        <v>70921</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5650021815170541</v>
+        <v>0.5683072877147947</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4666866008180318</v>
+        <v>0.4935085439561234</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6537603828036469</v>
+        <v>0.6511043348817511</v>
       </c>
     </row>
     <row r="15">
@@ -3711,16 +3711,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>43731</v>
+        <v>58649</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>43731</v>
+        <v>58649</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>43731</v>
+        <v>58649</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3732,16 +3732,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>34579</v>
+        <v>50276</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>34579</v>
+        <v>50276</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>34579</v>
+        <v>50276</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3753,16 +3753,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>78310</v>
+        <v>108924</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>78310</v>
+        <v>108924</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>78310</v>
+        <v>108924</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3786,67 +3786,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>12926</v>
+        <v>13526</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8018</v>
+        <v>9123</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17784</v>
+        <v>18940</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3684023834130568</v>
+        <v>0.3503481000284988</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2285369566398295</v>
+        <v>0.2363065158530887</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5068653905655334</v>
+        <v>0.490605193915186</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>9100</v>
+        <v>10469</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>5492</v>
+        <v>6765</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>14128</v>
+        <v>16054</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2842135354362265</v>
+        <v>0.2771722735391469</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1715182363093706</v>
+        <v>0.1791162352793107</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4412376708122193</v>
+        <v>0.4250488943662359</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>22026</v>
+        <v>23994</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>16161</v>
+        <v>17264</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>29686</v>
+        <v>31003</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.3282318715392648</v>
+        <v>0.3141611866840263</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.2408343893487853</v>
+        <v>0.226042640319123</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.4423803210994726</v>
+        <v>0.4059349133242768</v>
       </c>
     </row>
     <row r="17">
@@ -3857,67 +3857,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>22160</v>
+        <v>25080</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>17302</v>
+        <v>19666</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>27068</v>
+        <v>29483</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6315976165869432</v>
+        <v>0.6496518999715013</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4931346094344666</v>
+        <v>0.5093948060848139</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.7714630433601705</v>
+        <v>0.7636934841469112</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>22919</v>
+        <v>27300</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>17891</v>
+        <v>21715</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>26527</v>
+        <v>31004</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7157864645637735</v>
+        <v>0.7228277264608531</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5587623291877835</v>
+        <v>0.5749511056337646</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8284817636906295</v>
+        <v>0.8208837647206894</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>45080</v>
+        <v>52380</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>37420</v>
+        <v>45371</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>50945</v>
+        <v>59110</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.6717681284607352</v>
+        <v>0.6858388133159737</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.5576196789005277</v>
+        <v>0.5940650866757229</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.7591656106512148</v>
+        <v>0.7739573596808768</v>
       </c>
     </row>
     <row r="18">
@@ -3928,16 +3928,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>35086</v>
+        <v>38606</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>35086</v>
+        <v>38606</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>35086</v>
+        <v>38606</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3949,16 +3949,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>32019</v>
+        <v>37769</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>32019</v>
+        <v>37769</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>32019</v>
+        <v>37769</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3970,16 +3970,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>67106</v>
+        <v>76374</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>67106</v>
+        <v>76374</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>67106</v>
+        <v>76374</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -4003,25 +4003,25 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>23567</v>
+        <v>24617</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>17750</v>
+        <v>18500</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>29542</v>
+        <v>30494</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.4856533844932558</v>
+        <v>0.4965438896359325</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3657778666729787</v>
+        <v>0.3731631388214218</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6087901565603049</v>
+        <v>0.6150927535522343</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>21</v>
@@ -4030,40 +4030,40 @@
         <v>14055</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>9167</v>
+        <v>9489</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>19925</v>
+        <v>19278</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3064781294345037</v>
+        <v>0.296869662794448</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1998939883406824</v>
+        <v>0.2004386711646053</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.4344856334225071</v>
+        <v>0.4072026338362734</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>37622</v>
+        <v>38671</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>29755</v>
+        <v>30944</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>45515</v>
+        <v>47146</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.3985970917134845</v>
+        <v>0.3990062923224929</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.3152544063547626</v>
+        <v>0.3192798906623389</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.4822283089811034</v>
+        <v>0.4864427177492915</v>
       </c>
     </row>
     <row r="20">
@@ -4080,61 +4080,61 @@
         <v>24959</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>18984</v>
+        <v>19082</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>30776</v>
+        <v>31076</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.5143466155067441</v>
+        <v>0.5034561103640675</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.3912098434396951</v>
+        <v>0.3849072464477656</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.6342221333270214</v>
+        <v>0.6268368611785784</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>31804</v>
+        <v>33288</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>25934</v>
+        <v>28065</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>36692</v>
+        <v>37854</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.6935218705654963</v>
+        <v>0.7031303372055521</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.5655143665774927</v>
+        <v>0.5927973661637266</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.8001060116593175</v>
+        <v>0.7995613288353947</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>56763</v>
+        <v>58248</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>48870</v>
+        <v>49773</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>64630</v>
+        <v>65975</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.6014029082865154</v>
+        <v>0.6009937076775071</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.5177716910188966</v>
+        <v>0.5135572822507085</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.6847455936452375</v>
+        <v>0.680720109337661</v>
       </c>
     </row>
     <row r="21">
@@ -4145,16 +4145,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>48526</v>
+        <v>49576</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>48526</v>
+        <v>49576</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>48526</v>
+        <v>49576</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -4166,16 +4166,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>45859</v>
+        <v>47343</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>45859</v>
+        <v>47343</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>45859</v>
+        <v>47343</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -4187,16 +4187,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>94385</v>
+        <v>96919</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>94385</v>
+        <v>96919</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>94385</v>
+        <v>96919</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -4220,67 +4220,67 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>36958</v>
+        <v>45813</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>28973</v>
+        <v>37400</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>44420</v>
+        <v>55675</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.3494170684607408</v>
+        <v>0.364149604665843</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.2739258239854533</v>
+        <v>0.2972816544088168</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4199670680951707</v>
+        <v>0.4425378343795626</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>23871</v>
+        <v>29364</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>17800</v>
+        <v>21756</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>30733</v>
+        <v>37830</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.252976767825861</v>
+        <v>0.2564096861419342</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1886360788875847</v>
+        <v>0.1899700499149448</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3256899752572781</v>
+        <v>0.330334311754435</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>60830</v>
+        <v>75177</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>50429</v>
+        <v>62591</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>71562</v>
+        <v>86579</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.3039457816055118</v>
+        <v>0.3128098223452991</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.2519772393699843</v>
+        <v>0.2604378833608402</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.357573370681054</v>
+        <v>0.3602520040993659</v>
       </c>
     </row>
     <row r="23">
@@ -4291,67 +4291,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>68813</v>
+        <v>79995</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>61351</v>
+        <v>70133</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>76798</v>
+        <v>88408</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.6505829315392592</v>
+        <v>0.635850395334157</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.5800329319048293</v>
+        <v>0.5574621656204373</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.7260741760145466</v>
+        <v>0.7027183455911831</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>70491</v>
+        <v>85157</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>63629</v>
+        <v>76691</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>76562</v>
+        <v>92765</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.747023232174139</v>
+        <v>0.7435903138580658</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.6743100247427219</v>
+        <v>0.6696656882455653</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.8113639211124153</v>
+        <v>0.8100299500850554</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>139303</v>
+        <v>165152</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>128571</v>
+        <v>153750</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>149704</v>
+        <v>177738</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.6960542183944882</v>
+        <v>0.6871901776547009</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.6424266293189459</v>
+        <v>0.639747995900634</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.7480227606300156</v>
+        <v>0.7395621166391598</v>
       </c>
     </row>
     <row r="24">
@@ -4362,16 +4362,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>105771</v>
+        <v>125808</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>105771</v>
+        <v>125808</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>105771</v>
+        <v>125808</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -4383,16 +4383,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>94362</v>
+        <v>114521</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>94362</v>
+        <v>114521</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>94362</v>
+        <v>114521</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -4404,16 +4404,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>200133</v>
+        <v>240329</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>200133</v>
+        <v>240329</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>200133</v>
+        <v>240329</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -4437,67 +4437,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>61574</v>
+        <v>72666</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>53551</v>
+        <v>63406</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>72383</v>
+        <v>82298</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4957834412864573</v>
+        <v>0.4989810326789519</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4311819336732574</v>
+        <v>0.4353977212875535</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5828148096878443</v>
+        <v>0.5651263549065297</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>47741</v>
+        <v>51848</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>40097</v>
+        <v>43185</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>56206</v>
+        <v>61479</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.4067606549837836</v>
+        <v>0.3889397559445772</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.3416331240820251</v>
+        <v>0.3239516494445678</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.4788759972133242</v>
+        <v>0.4611863900437492</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>109315</v>
+        <v>124513</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>98306</v>
+        <v>110829</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>123207</v>
+        <v>137506</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.4525296584475371</v>
+        <v>0.4463909835320387</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4069541428673786</v>
+        <v>0.3973322347147841</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5100371304099605</v>
+        <v>0.4929731893673696</v>
       </c>
     </row>
     <row r="26">
@@ -4508,67 +4508,67 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>62621</v>
+        <v>72962</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>51812</v>
+        <v>63330</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>70644</v>
+        <v>82222</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5042165587135427</v>
+        <v>0.501018967321048</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.4171851903121565</v>
+        <v>0.4348736450934703</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.5688180663267427</v>
+        <v>0.5646022787124465</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>69629</v>
+        <v>81458</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>61164</v>
+        <v>71827</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>77273</v>
+        <v>90121</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.5932393450162163</v>
+        <v>0.6110602440554228</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.5211240027866758</v>
+        <v>0.5388136099562508</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.6583668759179749</v>
+        <v>0.6760483505554324</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>132250</v>
+        <v>154420</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>118358</v>
+        <v>141427</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>143259</v>
+        <v>168104</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.547470341552463</v>
+        <v>0.5536090164679613</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.4899628695900395</v>
+        <v>0.5070268106326304</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.5930458571326214</v>
+        <v>0.6026677652852159</v>
       </c>
     </row>
     <row r="27">
@@ -4579,16 +4579,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>124195</v>
+        <v>145628</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>124195</v>
+        <v>145628</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>124195</v>
+        <v>145628</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -4600,16 +4600,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>117370</v>
+        <v>133306</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>117370</v>
+        <v>133306</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>117370</v>
+        <v>133306</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -4621,16 +4621,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>241565</v>
+        <v>278933</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>241565</v>
+        <v>278933</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>241565</v>
+        <v>278933</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -4654,67 +4654,67 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
     </row>
     <row r="29">
@@ -4725,67 +4725,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>286420</v>
+        <v>347439</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>267514</v>
+        <v>327524</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>304521</v>
+        <v>369171</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.5463731495178916</v>
+        <v>0.5501812322109428</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.510307255451978</v>
+        <v>0.5186443961482414</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.5809015748057479</v>
+        <v>0.5845941408716442</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>474</v>
+        <v>569</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>317713</v>
+        <v>380564</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>301865</v>
+        <v>362632</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>334461</v>
+        <v>398720</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.6521214086158018</v>
+        <v>0.6589939323793537</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6195931041514716</v>
+        <v>0.6279420322653032</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.6864980051607779</v>
+        <v>0.6904332480665573</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>881</v>
+        <v>1062</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>604134</v>
+        <v>728004</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>577823</v>
+        <v>701583</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>630434</v>
+        <v>756885</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.5973118750184674</v>
+        <v>0.6021571441599545</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.5712979247049845</v>
+        <v>0.5803038512594035</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.6233149445503311</v>
+        <v>0.626045914808942</v>
       </c>
     </row>
     <row r="30">
@@ -4796,16 +4796,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -4817,16 +4817,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>1</v>
@@ -4838,16 +4838,16 @@
         <v>1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>1</v>
@@ -4923,7 +4923,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5330,19 +5330,19 @@
         <v>16281</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>10471</v>
+        <v>10376</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>25465</v>
+        <v>24306</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3885552708723573</v>
+        <v>0.3797492021531617</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2498908289675678</v>
+        <v>0.2420204483878191</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6077256320397243</v>
+        <v>0.5669312983890803</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>16</v>
@@ -5372,19 +5372,19 @@
         <v>28257</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>19956</v>
+        <v>20241</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>38890</v>
+        <v>38775</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3531709933182587</v>
+        <v>0.3489333166564085</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2494269429745898</v>
+        <v>0.2499490229367891</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.486074204910388</v>
+        <v>0.478826094915199</v>
       </c>
     </row>
     <row r="8">
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>25621</v>
+        <v>26592</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>16437</v>
+        <v>18567</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>31431</v>
+        <v>32497</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6114447291276427</v>
+        <v>0.6202507978468385</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3922743679602758</v>
+        <v>0.4330687016109195</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7501091710324325</v>
+        <v>0.7579795516121808</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>35</v>
@@ -5437,25 +5437,25 @@
         <v>0.80754454406095</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>51751</v>
+        <v>52723</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>41118</v>
+        <v>42205</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>60052</v>
+        <v>60739</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6468290066817411</v>
+        <v>0.6510666833435914</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5139257950896111</v>
+        <v>0.5211739050848012</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7505730570254101</v>
+        <v>0.7500509770632109</v>
       </c>
     </row>
     <row r="9">
@@ -5466,16 +5466,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>41902</v>
+        <v>42873</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>41902</v>
+        <v>42873</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>41902</v>
+        <v>42873</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -5508,16 +5508,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>80008</v>
+        <v>80980</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>80008</v>
+        <v>80980</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>80008</v>
+        <v>80980</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -5541,25 +5541,25 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>11432</v>
+        <v>13092</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7871</v>
+        <v>9413</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>14794</v>
+        <v>16978</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.523340583583852</v>
+        <v>0.5412239852738825</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3603290937150528</v>
+        <v>0.3891150036768607</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.6772032168133982</v>
+        <v>0.7018504155495663</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>9</v>
@@ -5568,40 +5568,40 @@
         <v>5386</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>2805</v>
+        <v>2342</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>8765</v>
+        <v>8700</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2518165660850052</v>
+        <v>0.2378733483431449</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1311488071565436</v>
+        <v>0.1034470314717936</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4098515532524536</v>
+        <v>0.3842704408961463</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>16818</v>
+        <v>18478</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>12144</v>
+        <v>13678</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>21816</v>
+        <v>23285</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3890139493953104</v>
+        <v>0.3945646887885125</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2808999015526302</v>
+        <v>0.2920661029049856</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.504634459810175</v>
+        <v>0.4972036084732419</v>
       </c>
     </row>
     <row r="11">
@@ -5612,67 +5612,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>10413</v>
+        <v>11098</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>7051</v>
+        <v>7212</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>13974</v>
+        <v>14777</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.4766594164161474</v>
+        <v>0.4587760147261173</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.3227967831866022</v>
+        <v>0.2981495844504335</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.6396709062849478</v>
+        <v>0.6108849963231394</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>16001</v>
+        <v>17255</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>12622</v>
+        <v>13941</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>18582</v>
+        <v>20299</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.748183433914995</v>
+        <v>0.7621266516568552</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.5901484467475463</v>
+        <v>0.6157295591038535</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8688511928434562</v>
+        <v>0.8965529685282063</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>26414</v>
+        <v>28353</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>21416</v>
+        <v>23546</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>31088</v>
+        <v>33153</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6109860506046895</v>
+        <v>0.6054353112114876</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.4953655401898252</v>
+        <v>0.5027963915267581</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7191000984473699</v>
+        <v>0.7079338970950145</v>
       </c>
     </row>
     <row r="12">
@@ -5683,37 +5683,37 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>24190</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>24190</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>24190</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>21845</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>21845</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>21845</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>36</v>
-      </c>
       <c r="K12" s="5" t="n">
-        <v>21387</v>
+        <v>22641</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>21387</v>
+        <v>22641</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>21387</v>
+        <v>22641</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -5725,16 +5725,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>43232</v>
+        <v>46831</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>43232</v>
+        <v>46831</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>43232</v>
+        <v>46831</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -5758,25 +5758,25 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>7028</v>
+        <v>9659</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2841</v>
+        <v>5077</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>10194</v>
+        <v>12700</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5927342931348584</v>
+        <v>0.6464594785784372</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2395764106278752</v>
+        <v>0.33982458237247</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.8597067329791728</v>
+        <v>0.8500329868154666</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>5</v>
@@ -5785,40 +5785,40 @@
         <v>4037</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1084</v>
+        <v>1373</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>8024</v>
+        <v>8003</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2364170630599007</v>
+        <v>0.2301211553152227</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.06349885589707677</v>
+        <v>0.07826802943985883</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4699399283781451</v>
+        <v>0.4562477808950461</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>11065</v>
+        <v>13695</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>6359</v>
+        <v>8661</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>16377</v>
+        <v>19772</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3824507614152971</v>
+        <v>0.4216226228032314</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2197839209038556</v>
+        <v>0.2666272587083128</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5660597545415883</v>
+        <v>0.6087129686058993</v>
       </c>
     </row>
     <row r="14">
@@ -5829,67 +5829,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4829</v>
+        <v>5282</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1663</v>
+        <v>2241</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>9016</v>
+        <v>9864</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4072657068651417</v>
+        <v>0.3535405214215627</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.1402932670208271</v>
+        <v>0.1499670131845333</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7604235893721247</v>
+        <v>0.6601754176275301</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>13037</v>
+        <v>13504</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>9050</v>
+        <v>9538</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>15990</v>
+        <v>16168</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7635829369400996</v>
+        <v>0.7698788446847773</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5300600716218549</v>
+        <v>0.5437522191049537</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9365011441029204</v>
+        <v>0.9217319705601412</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>17867</v>
+        <v>18787</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>12555</v>
+        <v>12710</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>22573</v>
+        <v>23821</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6175492385847029</v>
+        <v>0.5783773771967685</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4339402454584115</v>
+        <v>0.391287031394102</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7802160790961445</v>
+        <v>0.7333727412916872</v>
       </c>
     </row>
     <row r="15">
@@ -5900,16 +5900,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>11857</v>
+        <v>14941</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -5921,16 +5921,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>17074</v>
+        <v>17541</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -5942,16 +5942,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>28932</v>
+        <v>32482</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>28932</v>
+        <v>32482</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>28932</v>
+        <v>32482</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -5975,67 +5975,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>12564</v>
+        <v>13582</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8535</v>
+        <v>9738</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16631</v>
+        <v>17599</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4996922021485824</v>
+        <v>0.5072310459098661</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3394387691846157</v>
+        <v>0.3636752680197459</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6614704939122135</v>
+        <v>0.6572770144223445</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>9291</v>
+        <v>9797</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>6009</v>
+        <v>6541</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>12608</v>
+        <v>13086</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4281991132716518</v>
+        <v>0.4305258952493708</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2769596433186809</v>
+        <v>0.2874328193794923</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5810926357373938</v>
+        <v>0.5750874625435318</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>21854</v>
+        <v>23378</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>17062</v>
+        <v>18414</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>26988</v>
+        <v>28692</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.466575811314276</v>
+        <v>0.47199205484873</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3642710332562639</v>
+        <v>0.3717753528316054</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.5761848208325321</v>
+        <v>0.5792824738271952</v>
       </c>
     </row>
     <row r="17">
@@ -6046,67 +6046,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>12579</v>
+        <v>13194</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>8512</v>
+        <v>9177</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>16608</v>
+        <v>17038</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5003077978514178</v>
+        <v>0.4927689540901338</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.3385295060877864</v>
+        <v>0.3427229855776562</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6605612308153846</v>
+        <v>0.636324731980254</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>12406</v>
+        <v>12958</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>9089</v>
+        <v>9669</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>15688</v>
+        <v>16214</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5718008867283481</v>
+        <v>0.569474104750629</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.4189073642626063</v>
+        <v>0.4249125374564682</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.7230403566813192</v>
+        <v>0.7125671806205076</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>24986</v>
+        <v>26153</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>19852</v>
+        <v>20839</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>29778</v>
+        <v>31117</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5334241886857244</v>
+        <v>0.5280079451512703</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.4238151791674679</v>
+        <v>0.4207175261728049</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6357289667437361</v>
+        <v>0.6282246471683944</v>
       </c>
     </row>
     <row r="18">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>25143</v>
+        <v>26776</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>25143</v>
+        <v>26776</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>25143</v>
+        <v>26776</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -6138,16 +6138,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>21697</v>
+        <v>22755</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>21697</v>
+        <v>22755</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>21697</v>
+        <v>22755</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -6159,16 +6159,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>46840</v>
+        <v>49531</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>46840</v>
+        <v>49531</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>46840</v>
+        <v>49531</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -6192,67 +6192,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>7435</v>
+        <v>8072</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>4333</v>
+        <v>4508</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>11167</v>
+        <v>12228</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.3321586734146271</v>
+        <v>0.3278479366884877</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.1935789567007389</v>
+        <v>0.1830976096808144</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.4988995313705045</v>
+        <v>0.4966535511988642</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2496</v>
+        <v>3685</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>638</v>
+        <v>1272</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>5517</v>
+        <v>6912</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1580603343755104</v>
+        <v>0.2088490466071727</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.04039363200011917</v>
+        <v>0.07206936044490019</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.3493106713041059</v>
+        <v>0.3916816034579998</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>9931</v>
+        <v>11757</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>5948</v>
+        <v>7450</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>14615</v>
+        <v>16363</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.2601338015792998</v>
+        <v>0.2781674939762943</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.155814682991863</v>
+        <v>0.1762546472731229</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.3828300790949566</v>
+        <v>0.3871319310022786</v>
       </c>
     </row>
     <row r="20">
@@ -6263,67 +6263,67 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>16549</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>12393</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>20113</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.6721520633115122</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.5033464488011358</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.8169023903191857</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>14948</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>11216</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>18050</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0.6678413265853728</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0.5011004686294954</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0.8064210432992611</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="K20" s="5" t="n">
-        <v>13298</v>
+        <v>13961</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>10277</v>
+        <v>10734</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>15156</v>
+        <v>16374</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.8419396656244896</v>
+        <v>0.7911509533928273</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.6506893286958942</v>
+        <v>0.6083183965420003</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.9596063679998809</v>
+        <v>0.9279306395550997</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>28245</v>
+        <v>30510</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>23561</v>
+        <v>25904</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>32228</v>
+        <v>34817</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.7398661984207002</v>
+        <v>0.7218325060237055</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.6171699209050437</v>
+        <v>0.6128680689977213</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.844185317008137</v>
+        <v>0.8237453527268769</v>
       </c>
     </row>
     <row r="21">
@@ -6334,16 +6334,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>22383</v>
+        <v>24621</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>22383</v>
+        <v>24621</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>22383</v>
+        <v>24621</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -6355,16 +6355,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>15794</v>
+        <v>17646</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -6376,16 +6376,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>38176</v>
+        <v>42267</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>38176</v>
+        <v>42267</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>38176</v>
+        <v>42267</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -6415,61 +6415,61 @@
         <v>29581</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>22807</v>
+        <v>22601</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>36842</v>
+        <v>37241</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4527914429196261</v>
+        <v>0.4367783603850218</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.3490978750413135</v>
+        <v>0.3337208487081185</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.5639328260432511</v>
+        <v>0.5498920928993342</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>15039</v>
+        <v>17426</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>9839</v>
+        <v>12695</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>20768</v>
+        <v>23678</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.3239682037046092</v>
+        <v>0.350814864495768</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.2119439298220803</v>
+        <v>0.2555738553896479</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.4473672395000488</v>
+        <v>0.4766859145915652</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>44620</v>
+        <v>47007</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>35002</v>
+        <v>38165</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>53006</v>
+        <v>56318</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.3992781814928715</v>
+        <v>0.4004063155371658</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.3132105554097923</v>
+        <v>0.3250902343883053</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.4743163798639103</v>
+        <v>0.479715545511391</v>
       </c>
     </row>
     <row r="23">
@@ -6480,67 +6480,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>35749</v>
+        <v>38144</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>28488</v>
+        <v>30484</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>42523</v>
+        <v>45124</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.5472085570803739</v>
+        <v>0.5632216396149784</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.4360671739567489</v>
+        <v>0.4501079071006667</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.6509021249586865</v>
+        <v>0.6662791512918813</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>31383</v>
+        <v>32246</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>25654</v>
+        <v>25994</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>36583</v>
+        <v>36977</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.6760317962953908</v>
+        <v>0.6491851355042317</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.5526327604999507</v>
+        <v>0.5233140854084348</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.7880560701779196</v>
+        <v>0.7444261446103523</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>67132</v>
+        <v>70391</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>58746</v>
+        <v>61080</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>76750</v>
+        <v>79233</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.6007218185071285</v>
+        <v>0.5995936844628341</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.5256836201360896</v>
+        <v>0.5202844544886092</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.6867894445902077</v>
+        <v>0.6749097656116948</v>
       </c>
     </row>
     <row r="24">
@@ -6551,16 +6551,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>65330</v>
+        <v>67725</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>65330</v>
+        <v>67725</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>65330</v>
+        <v>67725</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>1</v>
@@ -6572,16 +6572,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>46422</v>
+        <v>49672</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>46422</v>
+        <v>49672</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>46422</v>
+        <v>49672</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1</v>
@@ -6593,16 +6593,16 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>111752</v>
+        <v>117398</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>111752</v>
+        <v>117398</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>111752</v>
+        <v>117398</v>
       </c>
       <c r="U24" s="6" t="n">
         <v>1</v>
@@ -6632,61 +6632,61 @@
         <v>31027</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>22990</v>
+        <v>23364</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>38685</v>
+        <v>39312</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.3895954479729838</v>
+        <v>0.3803241166502856</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.2886759370503201</v>
+        <v>0.2863984158090953</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4857585277628243</v>
+        <v>0.4818823992368125</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>10503</v>
+        <v>11822</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>6163</v>
+        <v>6970</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>16362</v>
+        <v>17266</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2009774947149787</v>
+        <v>0.2081276448290039</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.1179379143031134</v>
+        <v>0.122705675240968</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3130827354598268</v>
+        <v>0.3039665487653543</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>41530</v>
+        <v>42849</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>32504</v>
+        <v>33415</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>51263</v>
+        <v>52257</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.3148626340086576</v>
+        <v>0.3096426578730228</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.2464344942756952</v>
+        <v>0.2414675987037812</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.388653772612761</v>
+        <v>0.377625410649333</v>
       </c>
     </row>
     <row r="26">
@@ -6697,67 +6697,67 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>48612</v>
+        <v>50553</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>40954</v>
+        <v>42268</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>56649</v>
+        <v>58216</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.6104045520270163</v>
+        <v>0.6196758833497145</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.514241472237176</v>
+        <v>0.5181176007631874</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.71132406294968</v>
+        <v>0.7136015841909047</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>41757</v>
+        <v>44980</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>35898</v>
+        <v>39536</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>46097</v>
+        <v>49832</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.7990225052850213</v>
+        <v>0.7918723551709962</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6869172645401732</v>
+        <v>0.6960334512346456</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.8820620856968865</v>
+        <v>0.877294324759032</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>90369</v>
+        <v>95533</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>80636</v>
+        <v>86125</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>99395</v>
+        <v>104967</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.6851373659913425</v>
+        <v>0.6903573421269771</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.6113462273872391</v>
+        <v>0.622374589350667</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.7535655057243046</v>
+        <v>0.7585324012962187</v>
       </c>
     </row>
     <row r="27">
@@ -6768,16 +6768,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>79639</v>
+        <v>81580</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>79639</v>
+        <v>81580</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>79639</v>
+        <v>81580</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -6789,16 +6789,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>52260</v>
+        <v>56802</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>52260</v>
+        <v>56802</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>52260</v>
+        <v>56802</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -6810,16 +6810,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>131899</v>
+        <v>138382</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>131899</v>
+        <v>138382</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>131899</v>
+        <v>138382</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -6843,67 +6843,67 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>66080</v>
+        <v>71481</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>54849</v>
+        <v>60288</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>78050</v>
+        <v>84451</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.2797420285860966</v>
+        <v>0.2874848544914089</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.2321959483809797</v>
+        <v>0.2424683607083414</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3304118024216539</v>
+        <v>0.339650530879622</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>187419</v>
+        <v>198765</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>167434</v>
+        <v>179250</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>208024</v>
+        <v>218676</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.3525997894573501</v>
+        <v>0.3558486175747382</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.3150023636177863</v>
+        <v>0.3209115726201317</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.3913647415747844</v>
+        <v>0.3914969242414433</v>
       </c>
     </row>
     <row r="29">
@@ -6914,67 +6914,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>173977</v>
+        <v>182639</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>158241</v>
+        <v>164852</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>189114</v>
+        <v>198087</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.589122160890129</v>
+        <v>0.5893051957098844</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.5358390783859908</v>
+        <v>0.53191412887179</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.6403797198228557</v>
+        <v>0.6391501775708668</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>170139</v>
+        <v>177161</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>158169</v>
+        <v>164191</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>181370</v>
+        <v>188354</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.7202579714139035</v>
+        <v>0.7125151455085911</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6695881975783458</v>
+        <v>0.6603494691203782</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.7678040516190201</v>
+        <v>0.7575316392916587</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>344115</v>
+        <v>359800</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>323510</v>
+        <v>339889</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>364100</v>
+        <v>379315</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.6474002105426498</v>
+        <v>0.6441513824252617</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.6086352584252156</v>
+        <v>0.6085030757585567</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.6849976363822137</v>
+        <v>0.6790884273798686</v>
       </c>
     </row>
     <row r="30">
@@ -6985,16 +6985,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
@@ -7006,16 +7006,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>1</v>
@@ -7027,16 +7027,16 @@
         <v>1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>1</v>
